--- a/data/cox_xlsx/ORSTED.CO.xlsx
+++ b/data/cox_xlsx/ORSTED.CO.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="447">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -841,6 +841,9 @@
   </si>
   <si>
     <t>Deferred tax</t>
+  </si>
+  <si>
+    <t>Bond and bank debt LT</t>
   </si>
   <si>
     <t>Bonds and Bank loans</t>
@@ -13369,8 +13372,8 @@
       <c r="R115" s="15"/>
     </row>
     <row r="116" ht="15.0" customHeight="1">
-      <c r="A116" s="14" t="s">
-        <v>258</v>
+      <c r="A116" s="29" t="s">
+        <v>274</v>
       </c>
       <c r="B116" s="15">
         <v>137947.63</v>
@@ -13468,7 +13471,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B118" s="15"/>
       <c r="C118" s="15"/>
@@ -13502,7 +13505,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B119" s="15"/>
       <c r="C119" s="15"/>
@@ -13528,7 +13531,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B120" s="15"/>
       <c r="C120" s="15"/>
@@ -13720,7 +13723,7 @@
     </row>
     <row r="125" ht="15.0" customHeight="1">
       <c r="A125" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B125" s="15"/>
       <c r="C125" s="15"/>
@@ -13748,7 +13751,7 @@
     </row>
     <row r="126" ht="15.0" customHeight="1">
       <c r="A126" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B126" s="15"/>
       <c r="C126" s="15"/>
@@ -13774,7 +13777,7 @@
     </row>
     <row r="127" ht="15.0" customHeight="1">
       <c r="A127" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B127" s="15"/>
       <c r="C127" s="15"/>
@@ -13800,7 +13803,7 @@
     </row>
     <row r="128" ht="15.0" customHeight="1">
       <c r="A128" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B128" s="18">
         <v>240183.97</v>
@@ -13856,7 +13859,7 @@
     </row>
     <row r="129" ht="15.0" customHeight="1">
       <c r="A129" s="14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B129" s="16">
         <v>2959.73</v>
@@ -13904,7 +13907,7 @@
     </row>
     <row r="130" ht="15.0" customHeight="1">
       <c r="A130" s="17" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B130" s="18">
         <v>346405.1</v>
@@ -13960,7 +13963,7 @@
     </row>
     <row r="131" ht="15.0" customHeight="1">
       <c r="A131" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B131" s="15">
         <v>20900.01</v>
@@ -14016,7 +14019,7 @@
     </row>
     <row r="132" ht="15.0" customHeight="1">
       <c r="A132" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B132" s="22">
         <v>-14496.49</v>
@@ -14072,7 +14075,7 @@
     </row>
     <row r="133" ht="15.0" customHeight="1">
       <c r="A133" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B133" s="20">
         <v>-6542.72</v>
@@ -14122,7 +14125,7 @@
     </row>
     <row r="134" ht="15.0" customHeight="1">
       <c r="A134" s="14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B134" s="20">
         <v>-7953.77</v>
@@ -14172,7 +14175,7 @@
     </row>
     <row r="135" ht="15.0" customHeight="1">
       <c r="A135" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B135" s="15"/>
       <c r="C135" s="15"/>
@@ -14208,7 +14211,7 @@
     </row>
     <row r="136" ht="15.0" customHeight="1">
       <c r="A136" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B136" s="15"/>
       <c r="C136" s="15"/>
@@ -14232,7 +14235,7 @@
     </row>
     <row r="137" ht="15.0" customHeight="1">
       <c r="A137" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B137" s="15">
         <v>182977.87</v>
@@ -14288,7 +14291,7 @@
     </row>
     <row r="138" ht="15.0" customHeight="1">
       <c r="A138" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B138" s="15"/>
       <c r="C138" s="15"/>
@@ -14322,7 +14325,7 @@
     </row>
     <row r="139" ht="15.0" customHeight="1">
       <c r="A139" s="17" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B139" s="18">
         <v>189381.39</v>
@@ -14378,7 +14381,7 @@
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B140" s="15">
         <v>33148.62</v>
@@ -14490,7 +14493,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="17" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B142" s="18">
         <v>46227.74</v>
@@ -14546,7 +14549,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B143" s="18">
         <v>235609.12</v>
@@ -14602,7 +14605,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B144" s="18">
         <v>582014.22</v>
@@ -14658,7 +14661,7 @@
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B145" s="16">
         <v>1321.2</v>
@@ -14714,7 +14717,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B146" s="19">
         <v>0.14</v>
@@ -14770,7 +14773,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B147" s="16">
         <v>1321.06</v>
@@ -14826,7 +14829,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B148" s="30"/>
       <c r="C148" s="30"/>
@@ -14888,7 +14891,7 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B150" s="15"/>
       <c r="C150" s="15"/>
@@ -14942,7 +14945,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="14" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B152" s="15"/>
       <c r="C152" s="15"/>
@@ -14970,7 +14973,7 @@
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B153" s="15"/>
       <c r="C153" s="15">
@@ -15018,7 +15021,7 @@
     </row>
     <row r="154" ht="15.0" customHeight="1">
       <c r="A154" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B154" s="15"/>
       <c r="C154" s="15"/>
@@ -15042,7 +15045,7 @@
     </row>
     <row r="155" ht="15.0" customHeight="1">
       <c r="A155" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B155" s="15"/>
       <c r="C155" s="15"/>
@@ -15066,7 +15069,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B156" s="15">
         <v>18441.74</v>
@@ -15116,7 +15119,7 @@
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B157" s="15">
         <v>11932.24</v>
@@ -15166,7 +15169,7 @@
     </row>
     <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B158" s="15">
         <v>26408.17</v>
@@ -15216,7 +15219,7 @@
     </row>
     <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B159" s="15">
         <v>101007.2</v>
@@ -15266,7 +15269,7 @@
     </row>
     <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B160" s="15"/>
       <c r="C160" s="15">
@@ -15302,7 +15305,7 @@
     </row>
     <row r="161" ht="15.0" customHeight="1">
       <c r="A161" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B161" s="15"/>
       <c r="C161" s="15"/>
@@ -15326,7 +15329,7 @@
     </row>
     <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B162" s="15"/>
       <c r="C162" s="15"/>
@@ -15352,7 +15355,7 @@
     </row>
     <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B163" s="15"/>
       <c r="C163" s="15"/>
@@ -15376,7 +15379,7 @@
     </row>
     <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B164" s="16">
         <v>1882.46</v>
@@ -15414,7 +15417,7 @@
     </row>
     <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B165" s="16">
         <v>1607.21</v>
@@ -15448,7 +15451,7 @@
     </row>
     <row r="166" ht="15.0" customHeight="1">
       <c r="A166" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B166" s="16">
         <v>2643.35</v>
@@ -15482,7 +15485,7 @@
     </row>
     <row r="167" ht="15.0" customHeight="1">
       <c r="A167" s="14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B167" s="15">
         <v>16189.12</v>
@@ -15520,7 +15523,7 @@
     </row>
     <row r="168" ht="15.0" customHeight="1">
       <c r="A168" s="14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B168" s="15">
         <v>12696.29</v>
@@ -15546,7 +15549,7 @@
     </row>
     <row r="169" ht="15.0" customHeight="1">
       <c r="A169" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B169" s="19">
         <v>0.14</v>
@@ -15602,7 +15605,7 @@
     </row>
     <row r="170" ht="15.0" customHeight="1">
       <c r="A170" s="14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B170" s="16">
         <v>1321.2</v>
@@ -15658,7 +15661,7 @@
     </row>
     <row r="171" ht="15.0" customHeight="1">
       <c r="A171" s="14" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B171" s="16">
         <v>1321.06</v>
@@ -15714,7 +15717,7 @@
     </row>
     <row r="172" ht="15.0" customHeight="1">
       <c r="A172" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B172" s="19">
         <v>1.0</v>
@@ -15770,7 +15773,7 @@
     </row>
     <row r="173" ht="15.0" customHeight="1">
       <c r="A173" s="14" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B173" s="16">
         <v>7896.0</v>
@@ -15824,7 +15827,7 @@
     </row>
     <row r="174" ht="15.0" customHeight="1">
       <c r="A174" s="14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B174" s="15"/>
       <c r="C174" s="15"/>
@@ -15848,7 +15851,7 @@
     </row>
     <row r="175" ht="15.0" customHeight="1">
       <c r="A175" s="14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B175" s="15"/>
       <c r="C175" s="15"/>
@@ -15886,7 +15889,7 @@
     </row>
     <row r="176" ht="15.0" customHeight="1">
       <c r="A176" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B176" s="15"/>
       <c r="C176" s="15"/>
@@ -15924,7 +15927,7 @@
     </row>
     <row r="177" ht="15.0" customHeight="1">
       <c r="A177" s="14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B177" s="15"/>
       <c r="C177" s="15"/>
@@ -15962,7 +15965,7 @@
     </row>
     <row r="178" ht="15.0" customHeight="1">
       <c r="A178" s="14" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B178" s="15"/>
       <c r="C178" s="15"/>
@@ -16000,7 +16003,7 @@
     </row>
     <row r="179" ht="15.0" customHeight="1">
       <c r="A179" s="14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B179" s="15">
         <v>134272.0</v>
@@ -16875,7 +16878,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -17196,55 +17199,55 @@
         <v>39</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -17305,7 +17308,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -17383,7 +17386,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B20" s="16">
         <v>1511.86</v>
@@ -17427,7 +17430,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B21" s="15">
         <v>17058.6</v>
@@ -17457,7 +17460,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
@@ -17483,7 +17486,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B23" s="15">
         <v>35205.62</v>
@@ -17537,7 +17540,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B24" s="20">
         <v>-766.91</v>
@@ -17587,7 +17590,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B25" s="16">
         <v>3138.21</v>
@@ -17637,7 +17640,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B26" s="15"/>
       <c r="C26" s="20">
@@ -17689,7 +17692,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B27" s="16">
         <v>9138.59</v>
@@ -17745,7 +17748,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B28" s="22">
         <v>-14232.49</v>
@@ -17801,7 +17804,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B29" s="20">
         <v>-7683.19</v>
@@ -17857,7 +17860,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -17897,7 +17900,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -17937,7 +17940,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B32" s="21">
         <v>-9.41</v>
@@ -17991,7 +17994,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B33" s="20">
         <v>-1519.7</v>
@@ -18045,7 +18048,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B34" s="16">
         <v>1980.79</v>
@@ -18099,7 +18102,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B35" s="20">
         <v>-1819.25</v>
@@ -18153,7 +18156,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B36" s="20">
         <v>-4747.3</v>
@@ -18191,7 +18194,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B37" s="21">
         <v>-21.96</v>
@@ -18287,7 +18290,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B39" s="15"/>
       <c r="C39" s="15"/>
@@ -18311,7 +18314,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B40" s="15"/>
       <c r="C40" s="15"/>
@@ -18335,7 +18338,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
@@ -18359,7 +18362,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="17" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B42" s="18">
         <v>37233.45</v>
@@ -18415,7 +18418,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B43" s="22">
         <v>-85906.22</v>
@@ -18471,7 +18474,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B44" s="15">
         <v>19255.82</v>
@@ -18527,7 +18530,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
@@ -18579,7 +18582,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B46" s="19">
         <v>12.55</v>
@@ -18617,7 +18620,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
@@ -18657,7 +18660,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B48" s="20">
         <v>-326.21</v>
@@ -18691,7 +18694,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
@@ -18727,7 +18730,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B50" s="22">
         <v>-69316.55</v>
@@ -18783,7 +18786,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B51" s="15">
         <v>32023.5</v>
@@ -18839,7 +18842,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B52" s="19">
         <v>32.93</v>
@@ -18895,7 +18898,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B53" s="20">
         <v>-150.56</v>
@@ -18951,7 +18954,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B54" s="16">
         <v>127.03</v>
@@ -19007,7 +19010,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B55" s="15"/>
       <c r="C55" s="15"/>
@@ -19031,7 +19034,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B56" s="15"/>
       <c r="C56" s="15"/>
@@ -19071,7 +19074,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
@@ -19095,7 +19098,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B58" s="15"/>
       <c r="C58" s="15"/>
@@ -19119,7 +19122,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="17" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B59" s="24">
         <v>-104247.71</v>
@@ -19175,7 +19178,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B60" s="15">
         <v>30660.63</v>
@@ -19231,7 +19234,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B61" s="20">
         <v>-7052.73</v>
@@ -19287,7 +19290,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B62" s="20">
         <v>-1892.96</v>
@@ -19317,7 +19320,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B63" s="15"/>
       <c r="C63" s="15"/>
@@ -19345,7 +19348,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B64" s="15"/>
       <c r="C64" s="15"/>
@@ -19369,7 +19372,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B65" s="15"/>
       <c r="C65" s="15"/>
@@ -19411,7 +19414,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
@@ -19437,7 +19440,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B67" s="15">
         <v>93123.62</v>
@@ -19461,7 +19464,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B68" s="15">
         <v>0.0</v>
@@ -19513,7 +19516,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B69" s="15">
         <v>0.0</v>
@@ -19561,7 +19564,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B70" s="15"/>
       <c r="C70" s="15">
@@ -19609,7 +19612,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B71" s="20">
         <v>-3222.89</v>
@@ -19665,7 +19668,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B72" s="15"/>
       <c r="C72" s="15"/>
@@ -19699,7 +19702,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B73" s="15"/>
       <c r="C73" s="15"/>
@@ -19733,7 +19736,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B74" s="22">
         <v>-26068.59</v>
@@ -19789,7 +19792,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B75" s="15">
         <v>31792.95</v>
@@ -19821,7 +19824,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B76" s="20">
         <v>-337.19</v>
@@ -19859,7 +19862,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B77" s="20">
         <v>-1118.21</v>
@@ -19891,7 +19894,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B78" s="15"/>
       <c r="C78" s="15"/>
@@ -19927,7 +19930,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B79" s="15"/>
       <c r="C79" s="15"/>
@@ -19951,7 +19954,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B80" s="15"/>
       <c r="C80" s="15"/>
@@ -19975,7 +19978,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B81" s="15"/>
       <c r="C81" s="15"/>
@@ -19999,7 +20002,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B82" s="20">
         <v>-128.6</v>
@@ -20027,7 +20030,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B83" s="18">
         <v>115756.03</v>
@@ -20083,7 +20086,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B84" s="15"/>
       <c r="C84" s="15"/>
@@ -20117,7 +20120,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B85" s="15"/>
       <c r="C85" s="15"/>
@@ -20143,7 +20146,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B86" s="15"/>
       <c r="C86" s="15"/>
@@ -20179,7 +20182,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="17" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B87" s="18"/>
       <c r="C87" s="18"/>
@@ -20223,7 +20226,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B88" s="20">
         <v>-1184.08</v>
@@ -20277,7 +20280,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B89" s="15">
         <v>36579.76</v>
@@ -20333,7 +20336,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B90" s="15">
         <v>48741.77</v>
@@ -20383,7 +20386,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B91" s="15">
         <v>84549.16</v>
@@ -20439,7 +20442,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B92" s="15"/>
       <c r="C92" s="15"/>
@@ -20463,7 +20466,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="17" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B93" s="18">
         <v>47557.69</v>
@@ -20519,7 +20522,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="14" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B94" s="22">
         <v>-29562.81</v>
@@ -21481,7 +21484,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -21911,7 +21914,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -21989,7 +21992,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="31" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B20" s="32"/>
       <c r="C20" s="32"/>
@@ -22011,7 +22014,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="33" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B21" s="34">
         <v>301998.97</v>
@@ -22053,7 +22056,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="33" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B22" s="34">
         <v>414475.65</v>
@@ -22087,7 +22090,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="31" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B23" s="32"/>
       <c r="C23" s="32"/>
@@ -22109,7 +22112,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="33" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B24" s="34">
         <v>255711.12</v>
@@ -22151,7 +22154,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="33" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B25" s="34">
         <v>339086.62</v>
@@ -22185,7 +22188,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="31" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
@@ -22207,7 +22210,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="33" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B27" s="35">
         <v>193.54</v>
@@ -22249,7 +22252,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="33" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B28" s="35">
         <v>419.41</v>
@@ -22283,7 +22286,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="31" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B29" s="32"/>
       <c r="C29" s="32"/>
@@ -22305,7 +22308,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="33" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B30" s="36">
         <v>-29.21</v>
@@ -22347,7 +22350,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="33" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B31" s="36">
         <v>-10.63</v>
@@ -22381,7 +22384,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="31" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B32" s="32"/>
       <c r="C32" s="32"/>
@@ -22403,7 +22406,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="33" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B33" s="37">
         <v>0.0</v>
@@ -22445,7 +22448,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="33" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B34" s="37">
         <v>1.57</v>
@@ -22479,7 +22482,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="33" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B35" s="37">
         <v>0.0</v>
@@ -22521,7 +22524,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="33" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B36" s="37">
         <v>1.57</v>
@@ -22555,7 +22558,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="31" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B37" s="32"/>
       <c r="C37" s="32"/>
@@ -22577,7 +22580,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="33" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B38" s="38">
         <v>1.35</v>
@@ -22619,7 +22622,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="33" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B39" s="38">
         <v>3.1</v>
@@ -22653,7 +22656,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="31" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B40" s="32"/>
       <c r="C40" s="32"/>
@@ -22675,7 +22678,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="33" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B41" s="38">
         <v>1.36</v>
@@ -22717,7 +22720,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="33" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B42" s="38">
         <v>3.22</v>
@@ -22751,7 +22754,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="31" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B43" s="32"/>
       <c r="C43" s="32"/>
@@ -22773,7 +22776,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="33" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B44" s="38">
         <v>1.48</v>
@@ -22815,7 +22818,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="33" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B45" s="38">
         <v>2.48</v>
@@ -22849,7 +22852,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="31" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B46" s="32"/>
       <c r="C46" s="32"/>
@@ -22871,7 +22874,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="33" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B47" s="38">
         <v>8.12</v>
@@ -22911,7 +22914,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="33" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B48" s="38">
         <v>18.03</v>
@@ -22945,7 +22948,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="31" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B49" s="32"/>
       <c r="C49" s="32"/>
@@ -22967,7 +22970,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="33" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B50" s="38">
         <v>62.78</v>
@@ -23005,7 +23008,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="33" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B51" s="35">
         <v>235.76</v>
@@ -23039,7 +23042,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="31" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B52" s="32"/>
       <c r="C52" s="32"/>
@@ -23061,7 +23064,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="33" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B53" s="38">
         <v>26.25</v>
@@ -23103,7 +23106,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="33" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B54" s="38">
         <v>3.1</v>
@@ -23137,7 +23140,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="31" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B55" s="32"/>
       <c r="C55" s="32"/>
@@ -23159,7 +23162,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="33" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B56" s="38">
         <v>0.24</v>
@@ -23197,7 +23200,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="33" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B57" s="39">
         <v>-6.33</v>
@@ -23227,7 +23230,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="31" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B58" s="32"/>
       <c r="C58" s="32"/>
@@ -23249,7 +23252,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="33" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B59" s="38">
         <v>2.61</v>
@@ -23291,7 +23294,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="33" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B60" s="38">
         <v>3.15</v>
@@ -23325,7 +23328,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="31" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B61" s="32"/>
       <c r="C61" s="32"/>
@@ -23347,7 +23350,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="33" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B62" s="38">
         <v>8.47</v>
@@ -23389,7 +23392,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="33" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B63" s="38">
         <v>11.64</v>
@@ -23423,7 +23426,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="31" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B64" s="32"/>
       <c r="C64" s="32"/>
@@ -23445,7 +23448,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="33" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B65" s="38">
         <v>8.26</v>
@@ -23487,7 +23490,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="33" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B66" s="38">
         <v>14.24</v>
